--- a/reports/Debug-purgatory-20260105/For The Day (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Day (Actual)_Revenue.xlsx
@@ -124,7 +124,7 @@
     <t>D5209</t>
   </si>
   <si>
-    <t>D6720</t>
+    <t xml:space="preserve">D6720                    </t>
   </si>
   <si>
     <t>revenue</t>
